--- a/InputData/elec/PTTMbC/Plant Types That May be Curtailed.xlsx
+++ b/InputData/elec/PTTMbC/Plant Types That May be Curtailed.xlsx
@@ -1,43 +1,97 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26130"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\IA\elec\PTTMbC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\elec\PTTMbC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FADD2C0A-B5F8-41E5-90FB-6412B7D191AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C25A8819-10D2-4A61-BDDD-FD1F68E675E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3900" yWindow="3900" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="PTTMbC" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="145621"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+  <si>
+    <t>Source:</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Plant Type Used for Initial Guess at Marginal Dispatch Cost</t>
+  </si>
+  <si>
+    <t>None needed</t>
+  </si>
+  <si>
+    <t>hard coal</t>
+  </si>
+  <si>
+    <t>natural gas steam turbine</t>
+  </si>
+  <si>
+    <t>natural gas combined cycle</t>
+  </si>
+  <si>
+    <t>nuclear</t>
+  </si>
+  <si>
+    <t>hydro</t>
+  </si>
+  <si>
+    <t>wind</t>
+  </si>
+  <si>
+    <t>solar PV</t>
+  </si>
+  <si>
+    <t>solar thermal</t>
+  </si>
+  <si>
+    <t>biomass</t>
+  </si>
+  <si>
+    <t>geothermal</t>
+  </si>
+  <si>
+    <t>petroleum</t>
+  </si>
+  <si>
+    <t>natural gas peaker</t>
+  </si>
+  <si>
+    <t>lignite</t>
+  </si>
+  <si>
+    <t>offshore wind</t>
+  </si>
+  <si>
+    <t>crude oil</t>
+  </si>
+  <si>
+    <t>heavy or residual fuel oil</t>
+  </si>
+  <si>
+    <t>municipal solid waste</t>
+  </si>
+  <si>
+    <t>Unit: Boolean</t>
+  </si>
   <si>
     <t>Plant Types That May be Curtailed</t>
   </si>
   <si>
-    <t>Iowa</t>
-  </si>
-  <si>
-    <t>Source:</t>
-  </si>
-  <si>
-    <t>None needed</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
     <t>This file should use a flag of 1 for any plant type</t>
   </si>
   <si>
@@ -45,63 +99,6 @@
   </si>
   <si>
     <t>in a given hour.</t>
-  </si>
-  <si>
-    <t>Unit: Boolean</t>
-  </si>
-  <si>
-    <t>Plant Type Used for Initial Guess at Marginal Dispatch Cost</t>
-  </si>
-  <si>
-    <t>hard coal</t>
-  </si>
-  <si>
-    <t>natural gas steam turbine</t>
-  </si>
-  <si>
-    <t>natural gas combined cycle</t>
-  </si>
-  <si>
-    <t>nuclear</t>
-  </si>
-  <si>
-    <t>hydro</t>
-  </si>
-  <si>
-    <t>wind</t>
-  </si>
-  <si>
-    <t>solar PV</t>
-  </si>
-  <si>
-    <t>solar thermal</t>
-  </si>
-  <si>
-    <t>biomass</t>
-  </si>
-  <si>
-    <t>geothermal</t>
-  </si>
-  <si>
-    <t>petroleum</t>
-  </si>
-  <si>
-    <t>natural gas peaker</t>
-  </si>
-  <si>
-    <t>lignite</t>
-  </si>
-  <si>
-    <t>offshore wind</t>
-  </si>
-  <si>
-    <t>crude oil</t>
-  </si>
-  <si>
-    <t>heavy or residual fuel oil</t>
-  </si>
-  <si>
-    <t>municipal solid waste</t>
   </si>
 </sst>
 </file>
@@ -500,15 +497,12 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B3" t="s">
         <v>3</v>
@@ -516,27 +510,27 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -553,15 +547,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="B1" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -569,7 +563,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -577,7 +571,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -585,7 +579,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -593,7 +587,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -601,7 +595,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -609,7 +603,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -617,7 +611,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -625,7 +619,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -633,7 +627,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -641,7 +635,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -649,7 +643,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -657,7 +651,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -665,7 +659,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B15">
         <v>1</v>
@@ -673,7 +667,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -681,7 +675,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -689,7 +683,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B18">
         <v>0</v>
